--- a/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
+++ b/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
@@ -8,18 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +208,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>ICBC Standard Bank Plc — Cash Flow Summary by Year</a:t>
+              <a:t>ICBC Standard Bank Plc — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -401,6 +406,552 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>ICBC Standard Bank Plc — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ICBC Standard Bank Plc — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ICBC Standard Bank Plc — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>ICBC Standard Bank Plc — Pillar 3 Key Metrics by Year</a:t>
             </a:r>
           </a:p>
@@ -428,7 +979,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
@@ -446,12 +997,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,7 +1012,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
@@ -479,12 +1030,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,7 +1045,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
@@ -512,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,7 +1078,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
@@ -545,12 +1096,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,7 +1111,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
@@ -578,12 +1129,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,7 +1144,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
@@ -611,12 +1162,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,7 +1244,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -715,10 +1266,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -728,6 +1279,72 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1665,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1701,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary ($m)</t>
+          <t>Balance Sheet Summary ($m)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1768,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,294 +1797,294 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Cash flows (used in)/from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-1780.3</v>
+        <v>37800.7</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>128.1</v>
+        <v>26600.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-2150.7</v>
+        <v>23247.1</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-1137.3</v>
+        <v>22627.3</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2255.8</v>
+        <v>26268.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cash flows (used in)/from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2255.8</v>
+        <v>26268.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-1137.3</v>
+        <v>22627.3</v>
       </c>
       <c r="L6" t="n">
-        <v>-2150.7</v>
+        <v>23247.1</v>
       </c>
       <c r="M6" t="n">
-        <v>128.1</v>
+        <v>26600.4</v>
       </c>
       <c r="N6" t="n">
-        <v>-1780.3</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>37800.7</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>13.47</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>15.7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>16.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>14.6</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>12.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-18</v>
+        <v>1828</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-16.4</v>
+        <v>1303</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-6.9</v>
+        <v>771.3</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-15.5</v>
+        <v>818.6</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-12.5</v>
+        <v>1608.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-12.5</v>
+        <v>1608.7</v>
       </c>
       <c r="K7" t="n">
-        <v>-15.5</v>
+        <v>818.6</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.9</v>
+        <v>771.3</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.4</v>
+        <v>1303</v>
       </c>
       <c r="N7" t="n">
-        <v>-18</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>1828</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>15.35</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>17.5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>18.5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>16</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>13.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Cash flows used in financing activities</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-63.6</v>
+        <v>35669.3</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-70.59999999999999</v>
+        <v>24656.7</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-22.6</v>
+        <v>21376.2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-21.9</v>
+        <v>20945.3</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-24.7</v>
+        <v>24898.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cash flows used in financing activities</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-24.7</v>
+        <v>24898.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.9</v>
+        <v>20945.3</v>
       </c>
       <c r="L8" t="n">
-        <v>-22.6</v>
+        <v>21376.2</v>
       </c>
       <c r="M8" t="n">
-        <v>-70.59999999999999</v>
+        <v>24656.7</v>
       </c>
       <c r="N8" t="n">
-        <v>-63.6</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>35669.3</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>18.28</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>20.2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>21.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>18.1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of the year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>902.6</v>
+        <v>2131.4</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2762</v>
+        <v>1943.7</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2744.4</v>
+        <v>1870.9</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4990.4</v>
+        <v>1682</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>6122.5</v>
+        <v>1370</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of the year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6122.5</v>
+        <v>1370</v>
       </c>
       <c r="K9" t="n">
-        <v>4990.4</v>
+        <v>1682</v>
       </c>
       <c r="L9" t="n">
-        <v>2744.4</v>
+        <v>1870.9</v>
       </c>
       <c r="M9" t="n">
-        <v>2762</v>
+        <v>1943.7</v>
       </c>
       <c r="N9" t="n">
-        <v>902.6</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>2131.4</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>5.09</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>7.7</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>7.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>6.9</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>5.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>207</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>206</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>165.3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>226.7</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>197.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary ($m)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>163.8</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>183.3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>136.4</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>122.8</v>
       </c>
     </row>
@@ -1478,201 +2119,813 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>739.8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>572.1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>558</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>809.9</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>466</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>466</v>
+      </c>
+      <c r="S13" t="n">
+        <v>809.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>558</v>
+      </c>
+      <c r="U13" t="n">
+        <v>572.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>739.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-443.9</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-382.4</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-397.6</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-373.6</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-348.1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-348.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-373.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-397.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-382.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-443.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit attributable to equity shareholders</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit attributable to equity shareholders</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>224.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1943.7</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1870.9</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1682</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1301.5</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>1301.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1370</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1682</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1870.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1943.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>241.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-54.2</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-62.1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-62.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-54.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows (used in)/from operating activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-1780.3</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-2150.7</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-1137.3</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2255.8</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Cash flows (used in)/from operating activities</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>2255.8</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-1137.3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-2150.7</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-1780.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-18</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Cash flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-63.6</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-70.59999999999999</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Cash flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-70.59999999999999</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-63.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of the year</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>902.6</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2762</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2744.4</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>4990.4</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of the year</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>4990.4</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>2744.4</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2762</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>902.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>12.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>14.6%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>16.9%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>15.7%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>13.47%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>13.3%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>16.0%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>15.35%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>18.1%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>21.1%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>20.2%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>18.28%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>5.6%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>6.9%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>7.7%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>7.7%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>5.09%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>197.3%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>226.7%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>165.3%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>206.0%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>207%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>122.8%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>136.4%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>183.3%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>163.8%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. All amounts are in USD ($m), the reporting currency used throughout ICBC Standard Bank Plc's Annual Reports and Pillar 3 Disclosures.</t>
         </is>
@@ -1680,7 +2933,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1688,6 +2941,760 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, $m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2229.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2086.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2039.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1864.6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1558.4</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is 'Total eligible capital' from Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is 'Capital Adequacy ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, $m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>14902.7</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11500.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>9653.200000000001</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9251</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>8526.299999999999</v>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Group (consolidated basis), $m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 ($m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 ($m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 ($m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 ($m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts by category</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3495</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2736.3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2692.2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1770.9</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk, counterparty credit risk and dilution risk, combined (FY2021's older disclosure format only - not separable into the components above; derived from Table 6's capital requirement ÷8%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5023.6</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2843.7</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2109.9</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Of which credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>460.4</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>276</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>193.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Settlement risk</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Securitisation exposures in the non-trading book</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (position, foreign exchange and commodities)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>4799.2</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4464.4</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3475.5</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>4277.5</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>3681.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1402.4</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1455.1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1375.5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>818.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Amounts below thresholds for deduction (subject to 250% risk weight, for information)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>14902.7</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11500.1</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>9653.200000000001</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>9251</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8526.299999999999</v>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.6 (UK OV1 - Overview of risk-weighted exposure amounts) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.6-7 (UK OV1) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.24 (Table 6: ICBCS - Capital Requirements, pre-UK-OV1 format) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
+Note: FY2021's Pillar 3 document predates the UK OV1 template and combines credit, counterparty credit and dilution risk into one 'standardised approach' capital-requirement line, so it cannot be split into 'Credit risk (excluding CCR)' and 'Counterparty credit risk (CCR)' the way later years' disclosures are - shown as its own combined line instead of blended into either category. All FY2021 category figures are derived (disclosed capital requirement ÷ 8%, the standard CRR conversion), not directly disclosed as RWA amounts; they sum to $8,526.25m, which rounds to the disclosed Total RWA of $8,526.3m. FY2021's document has no 'Securitisation exposures' or 'Amounts below thresholds for deduction' line at all (genuinely not disclosed in that format, left blank rather than assumed zero).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A16:F16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1830,7 +3837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1995,7 +4002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2156,7 +4163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2283,6 +4290,2064 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Group (consolidated basis), $m unless stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 ($m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 ($m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 ($m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 ($m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances with central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>764.5</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2674.1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2635.9</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4856.1</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>6056.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Due from banks and other financial institutions</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>5438.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3727.2</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2248.4</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2182.3</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>2306.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets held for trading</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1413.4</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1211.9</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1278.5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>702.7</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2455.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Non-trading financial assets at fair value through profit or loss</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1017.6</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>689</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2856.6</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>2193.7</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1972.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial assets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>8686.4</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3911.2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3383.2</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4968</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>4392.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Reverse repurchase agreements</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>4987.3</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3526.8</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2936</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2614.6</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>2287.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>771.3</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>818.6</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1608.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Financial investments</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3721.7</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3176.9</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2052.8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1293.4</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>925.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Current tax assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Other assets (incl. non-financial commodities inventory held for trading)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>9848.200000000001</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>6289.1</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>4997.7</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2957.2</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>4211.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>37800.7</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>26600.4</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>23247.1</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>22627.3</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>26268.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Financial liabilities held for trading</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1876.9</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>938</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1634.7</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1295.2</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1566.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Non-trading financial liabilities at fair value through profit or loss</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>7342.6</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>6975.3</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3744</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2951.2</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2099.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>7368.4</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>4194.9</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3782.3</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>5352.8</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>5050.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Due to banks and other financial institutions</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>7761.1</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>4731.3</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>6553.2</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>6221.9</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>11646.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Repurchase agreements</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1079.1</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>1080.4</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>853.1</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>530.1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>693.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Due to customers</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2386.8</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1431</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1077.1</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1736.5</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1235.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Current tax liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated debt</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>251.9</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>245.4</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>250.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities (incl. precious metal payables)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>7599.3</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5056.4</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3481.8</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2608.7</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2352.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>35669.3</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>24656.7</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>21376.2</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>20945.3</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>24898.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Share capital (and share premium pre-FY2021 restructure)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1083.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>887.9</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>700.2</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>627.4</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Total equity (attributable to ordinary shareholders)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2131.4</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1943.7</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1870.9</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1682</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>37800.7</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>26600.4</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>23247.1</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>22627.3</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>26268.5</v>
+      </c>
+    </row>
+    <row r="36" ht="110" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
+FY2025 &amp; FY2024: ICBC Standard Bank Consolidated Annual Report 2025, p.64 (Consolidated balance sheet) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/consolidatedannualreport2025.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Consolidated Annual Report 2023, p.61 (7. Consolidated balance sheet) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023annualreportyasuo.pdf
+FY2021: ICBC Standard Bank Consolidated Annual Report 2021, p.61 (6. Consolidated balance sheet) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/Consolidated_Annual_Report_2021.pdf
+Note: an 'Ordinary share premium' line ($996.0m at FY2020) was eliminated via a June 2021 share premium restructure (cancelled and transferred to retained earnings) - by FY2021 year-end onward, share capital and premium are a single, fully-merged line.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A36:F36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Consolidated Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Group (consolidated basis), $m unless stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 ($m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 ($m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 ($m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 ($m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>730.8</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>613.4</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>524.7</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-482.7</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-449.5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-370.8</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-156.3</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-23.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commission expenses</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-27.1</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-27.1</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-19.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fees and commission</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net trading revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>257</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>314</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>400.6</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>260.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Net gain on non-trading financial assets/liabilities at fair value through profit or loss</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Recoveries/(losses) on commodity inventory intermediation</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Recoveries on commodity reverse repurchase agreements</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Non-interest revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>491.7</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>404.1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>711.4</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>739.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>572.1</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>558</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>809.9</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Credit impairment charges/(recoveries)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-60.8</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Income after credit impairments</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>724.8</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>569.4</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>608.2</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>749.1</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>468.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-279.2</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-248.5</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-247.8</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-223.9</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-216.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-156.8</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-130.8</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-145.9</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-147.9</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-127.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Restructuring costs and other impairments</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Indirect taxation</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-443.9</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-382.4</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-397.6</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-373.6</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-348.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Profit before taxation</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>280.9</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>120.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Income tax charge</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>-56</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-22.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Profit attributable to equity shareholders</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation reserve</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedging reserve, net</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-19.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Changes in fair value of debt instruments measured at FVOCI</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Gains/(losses) attributable to own credit risk</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(losses) for the year</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-17.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income attributable to equity shareholders</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="36" ht="130" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
+FY2025 &amp; FY2024: ICBC Standard Bank Consolidated Annual Report 2025, p.65 (Consolidated income statement) and p.66 (Consolidated statement of comprehensive income) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/consolidatedannualreport2025.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Consolidated Annual Report 2023, p.62-63 (8-9. Consolidated income statement / statement of comprehensive income) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023annualreportyasuo.pdf
+FY2021: ICBC Standard Bank Consolidated Annual Report 2021, p.62-63 (7-8. Consolidated income statement / statement of comprehensive income) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/Consolidated_Annual_Report_2021.pdf
+Note: 'Recoveries/(losses) on commodity inventory intermediation' and 'Recoveries on commodity reverse repurchase agreements' are one-off lines that only appear in the FY2021/FY2022 income statement structure (and 'Restructuring costs and other impairments' only in FY2021) - blank cells indicate that year's report did not disclose that specific line, not a genuine zero. FY2021's 'Other comprehensive income/(losses) for the year' ($(17.9)m) is derived (Total comprehensive income less Profit for the year) since that year's report does not show an explicit OCI subtotal row - the disclosed OCI component lines sum to $(18.0)m, a $0.1m rounding difference reproduced as disclosed, not forced to match.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A36:F36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Consolidated Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Group (consolidated basis), $m, chronological roll-forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital (and premium pre-restructure)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow hedging reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FVOCI reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FX translation reserve</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Net investment hedge reserve</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Own credit reserve</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2021 (FY2021's own opening)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2079.5</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>-950.4</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1301.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total comprehensive gains/(losses) for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Share premium restructure (cancellation of share premium, transferred to retained earnings)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-996</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n">
+        <v>996</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Coupon payment on other equity instruments</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2021 (FY2021 close = FY2022 opening)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total comprehensive gains/(losses) for the year</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>324.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Coupon payment on other equity instruments</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2022 (FY2022 close = FY2023 opening)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>437</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Total comprehensive gains/(losses) for the year</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>201.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Coupon payment on other equity instruments</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2023 (FY2023 close = FY2024 opening)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>611.9</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1870.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Total comprehensive gains/(losses) for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>134.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Dividend payment on ordinary share capital</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-49.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Coupon payment on other equity instruments</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2024 (FY2024 close = FY2025 opening)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>706.3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1943.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Total comprehensive gains for the year</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>241.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Dividend payment on ordinary share capital</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-41.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Coupon payment on other equity instruments</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2025 (FY2025 close)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>877</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>2131.4</v>
+      </c>
+    </row>
+    <row r="24" ht="140" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
+FY2025 &amp; FY2024 movements: ICBC Standard Bank Consolidated Annual Report 2025, p.67 (Consolidated statement of changes in shareholders' equity) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/consolidatedannualreport2025.pdf
+FY2023 &amp; FY2022 movements: ICBC Standard Bank Consolidated Annual Report 2023, p.64 (10. Consolidated statement of changes in shareholders' equity) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023annualreportyasuo.pdf
+FY2021 movements: ICBC Standard Bank Consolidated Annual Report 2021, p.64 (9. Consolidated statement of changes in shareholders' equity) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/Consolidated_Annual_Report_2021.pdf
+Reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total equity - zero plug rows needed anywhere across all 5 years. The June 2021 share premium restructure (cancellation of the $996.0m share premium account, transferred to retained earnings) is shown as an explicit, net-zero movement row rather than absorbed silently. 'Own credit reserve' genuinely nets to $0.0m from FY2024 year-end onward (shown as '-' in the Bank's own tables), not a blank/inapplicable cell.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:J24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3101,16 +7166,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3121,429 +7186,345 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — CET1 Capital</t>
+          <t>ICBC Standard Bank Plc — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, $m</t>
+          <t>ICBC Standard Bank Group (consolidated basis), $m unless stated</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 ($m)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 ($m)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 ($m)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 ($m)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 ($m)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1819.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1676.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1629.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1454.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1148.4</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is 'Total Common Equity Tier I' from Table 5 (Capital Resources), the transitional-basis equivalent of the UK KM1 template row used from FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>12.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>13.47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Gross balances subject to the three-stage ECL model</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12-month ECL)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>13357.1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>11465.1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9323.6</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>10617.5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>11586.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL, not credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL, credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Purchased or originated credit-impaired (POCI)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total gross balances subject to ECL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>13401.1</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11470.4</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9334.4</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10750.7</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11653.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Credit loss allowance, by stage (year-end balance)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12-month ECL)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL, not credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL, credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Purchased or originated credit-impaired (POCI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-51.4</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total credit loss allowance</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-34.7</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-66.59999999999999</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-5.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Derived coverage ratio</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Total credit loss allowance / total gross balances subject to ECL</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="140" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
+FY2025 &amp; FY2024: ICBC Standard Bank Consolidated Annual Report 2025, p.159-160 (Note 37.4 Credit risk - Analysis of gross balances/Movements in credit loss allowances) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/consolidatedannualreport2025.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Consolidated Annual Report 2023, p.147-148 (Note 37 Risk management - same tables) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023annualreportyasuo.pdf
+FY2021: ICBC Standard Bank Consolidated Annual Report 2021, p.143-144 (Note 37 Risk management - same tables) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/Consolidated_Annual_Report_2021.pdf
+Note: coverage is across the Group's entire ECL-model population (cash, interbank placements, reverse repos, loans and advances, financial investments, commitments/guarantees) - not restricted to customer loans, since that is how the Group's own credit-risk note is structured. FY2021's own disclosure does not break out a separate POCI column (leave blank, not zero) or a distinct 'Sub-standard/Doubtful/Loss' Stage 3 sub-split; FY2021 Stage 3 total is genuinely nil. The derived coverage ratio (total allowance / total gross balances) is computed here for a comparable cross-year signal, not itself a disclosed figure.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, $m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1979.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1836.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1789.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1614.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1308.4</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>15.35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3569,7 +7550,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total Capital</t>
+          <t>ICBC Standard Bank Plc — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3615,29 +7596,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2229.5</v>
+        <v>1819.5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>2086.1</v>
+        <v>1676.1</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2039.1</v>
+        <v>1629.1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1864.6</v>
+        <v>1454.6</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1558.4</v>
+        <v>1148.4</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is 'Total eligible capital' from Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+          <t>Note: FY2021 figure is 'Total Common Equity Tier I' from Table 5 (Capital Resources), the transitional-basis equivalent of the UK KM1 template row used from FY2022 onward.</t>
         </is>
       </c>
     </row>
@@ -3666,7 +7647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3680,7 +7661,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total Capital Ratio</t>
+          <t>ICBC Standard Bank Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3726,44 +7707,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>18.28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is 'Capital Adequacy ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>13.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
@@ -3773,9 +7747,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3801,7 +7774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total RWAs</t>
+          <t>ICBC Standard Bank Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3847,23 +7820,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>14902.7</v>
+        <v>1979.5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>11500.1</v>
+        <v>1836.1</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9653.200000000001</v>
+        <v>1789.1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>9251</v>
+        <v>1614.6</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>8526.299999999999</v>
+        <v>1308.4</v>
       </c>
     </row>
     <row r="6" ht="100" customHeight="1">

--- a/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
+++ b/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4053,7 +4054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4073,14 +4074,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Tier 1 Ratio</t>
+          <t>ICBC Standard Bank Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, $m</t>
         </is>
       </c>
     </row>
@@ -4149,74 +4150,45 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>15.35%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>15.94%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>18.52%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>15.59%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row; same for FY2020-FY2015. Tier 1 ratio equals the CET1 ratio exactly for FY2015-FY2018 (no Additional Tier 1 capital existed yet).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1979.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1836.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1789.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1614.6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1308.4</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1232.9</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1108.3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>928.6</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
@@ -4233,9 +4205,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A7:L7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4267,14 +4238,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total Capital</t>
+          <t>ICBC Standard Bank Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, $m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -4343,47 +4314,69 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>2229.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>2086.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>2039.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1864.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1558.4</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1482.9</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1358.3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1446.1</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>1575.4</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>1227.3</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1449.6</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>15.18%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>15.94%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>18.52%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>15.59%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021-FY2015 figures are each year's own 'Total eligible capital' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+          <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row; same for FY2020-FY2015. Tier 1 ratio equals the CET1 ratio exactly for FY2015-FY2018 (no Additional Tier 1 capital existed yet).</t>
         </is>
       </c>
     </row>
@@ -4439,14 +4432,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total Capital Ratio</t>
+          <t>ICBC Standard Bank Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, $m</t>
         </is>
       </c>
     </row>
@@ -4515,69 +4508,47 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>21.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>18.26%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>19.54%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>22.25%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>19.97%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>19.3%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>19.13%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2229.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2086.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2039.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1864.6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1558.4</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1482.9</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1358.3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1446.1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1575.4</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>1227.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1449.6</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021-FY2015 figures are each year's own 'Capital Adequacy ratio' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+          <t>Note: FY2021-FY2015 figures are each year's own 'Total eligible capital' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
         </is>
       </c>
     </row>
@@ -4608,6 +4579,200 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>18.26%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>19.54%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>22.25%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>19.97%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>19.3%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>19.13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021-FY2015 figures are each year's own 'Capital Adequacy ratio' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
+FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.26 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
+FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.27 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
+FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
+FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
+FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.23 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
+FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
+Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A7:L7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4771,7 +4936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5279,7 +5444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5508,272 +5673,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A6:L6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, $m / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value (average) ($m)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>5294.2</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>5216.2</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>5704.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>6280.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>5027</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>4371</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>4856</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>4458</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>4322</v>
-      </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value ($m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>2777.2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>2422.5</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>2926.2</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2425</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>2426</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>2509</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>2062</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>3126</v>
-      </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>197.3%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>226.7%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>165.3%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>206.0%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>207%</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>180%</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>195%</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>217%</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>145%</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>159%</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: LCR figures are averages of month-end observations over the 12 months preceding each year-end. FY2021-FY2017 figures are each year's own 31 December quarter-end column of the 'Consolidated Liquidity Coverage Ratio for ICBCS (Group)' table, the same consolidated-Group basis used by the later UK KM1 template rows. FY2016's Pillar 3 document discloses only a single point-in-time LCR% as at 31 December 2016 (159%, PRA minimum 80% that year) with no HQLA/net-outflow $ breakdown and not framed as a 12-month average - a narrower disclosure format than later years', shown with blank $m cells rather than a fabricated breakdown. FY2015's Pillar 3 document discusses the LCR requirement only qualitatively, with no numeric LCR%, HQLA or net-outflow figure disclosed at all that year (the EBA/PRA quarterly LCR disclosure tables used from FY2017 onward were not yet in place) - a genuine self-skip, not a search failure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
-FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
-FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.31 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
-FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.29 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
-FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
-FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
-FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
-Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A9:L9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5805,7 +5704,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — NSFR</t>
+          <t>ICBC Standard Bank Plc — LCR</t>
         </is>
       </c>
     </row>
@@ -5881,105 +5780,141 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding ($m)</t>
+          <t>Total high-quality liquid assets (HQLA), weighted value (average) ($m)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9393</v>
+        <v>5294.2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8348.6</v>
+        <v>5216.2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7963.4</v>
+        <v>5704.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>8417.6</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
+        <v>6280.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>5027</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4371</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4856</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4458</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>4322</v>
+      </c>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding ($m)</t>
+          <t>Total net cash outflows, adjusted value ($m)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>7736.7</v>
+        <v>2777.2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6118.4</v>
+        <v>2422.5</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4462</v>
+        <v>3561.5</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>5266.3</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
+        <v>2926.2</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2425</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>2426</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>2509</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>2062</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>3126</v>
+      </c>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+          <t>Liquidity Coverage Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>197.3%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>226.7%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>165.3%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>206.0%</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>207%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>195%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>217%</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>145%</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>159%</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not publicly disclosed</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR was not a UK Pillar 3 disclosure requirement until 1 January 2022 (the UK NSFR regime's effective date), so no FY2015-FY2021 figures are available in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025). FY2015's own Pillar 3 document explicitly notes 'the NSFR is expected to go live in January 2018' (an EU timeline later superseded by the UK's own 1 January 2022 implementation) - confirming this is a genuine regulatory-timeline gap, not a missed disclosure. Balances shown for FY2022 onward are averages of the four quarter-ends preceding each year-end.</t>
+          <t>Note: LCR figures are averages of month-end observations over the 12 months preceding each year-end. FY2021-FY2017 figures are each year's own 31 December quarter-end column of the 'Consolidated Liquidity Coverage Ratio for ICBCS (Group)' table, the same consolidated-Group basis used by the later UK KM1 template rows. FY2016's Pillar 3 document discloses only a single point-in-time LCR% as at 31 December 2016 (159%, PRA minimum 80% that year) with no HQLA/net-outflow $ breakdown and not framed as a 12-month average - a narrower disclosure format than later years', shown with blank $m cells rather than a fabricated breakdown. FY2015's Pillar 3 document discusses the LCR requirement only qualitatively, with no numeric LCR%, HQLA or net-outflow figure disclosed at all that year (the EBA/PRA quarterly LCR disclosure tables used from FY2017 onward were not yet in place) - a genuine self-skip, not a search failure.</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5924,14 @@
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
 FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
+FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
+FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.31 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
+FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.29 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
+FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
+FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
+FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
+Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
         </is>
       </c>
     </row>
@@ -6003,6 +5945,246 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, $m / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding ($m)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>9393</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8348.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7963.4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>8417.6</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding ($m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>7736.7</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6118.4</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4462</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5266.3</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>122.8%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>136.4%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>183.3%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>163.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: OMISSION CORRECTED 2026-09-17 (KM1-017): the four NSFR percentages for FY2025-FY2022 were MISSING from this sheet until this ticket. The available and required stable funding amounts were present for those four years but the ratio row carried no value for any of them - it was built from a comprehension that assigned 'Not disclosed' to every year EXCEPT FY2025-FY2022, and then never assigned those four anything at all, so they rendered blank. The bank does disclose them: they are row 20 of its own UK KM1 template in each year's edition (FY2025 122.8%, FY2024 136.4%, FY2023 183.3%, FY2022 163.8%), the same table this workbook's KM1 Key Metrics sheet reproduces and the same table the stable-funding amounts on the rows above already came from. Nothing was re-derived: each figure is transcribed from the edition in which that year is the reporting year. The omission came to light on 2026-09-17, when this workbook gained a KM1 Key Metrics sheet reproducing row 20 of the same table for the same years and so placed a second, independent transcription of each of those four figures beside this sheet's.
+NSFR was not a UK Pillar 3 disclosure requirement until 1 January 2022 (the UK NSFR regime's effective date), so no FY2015-FY2021 figures are available in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025). FY2015's own Pillar 3 document explicitly notes 'the NSFR is expected to go live in January 2018' (an EU timeline later superseded by the UK's own 1 January 2022 implementation) - confirming this is a genuine regulatory-timeline gap, not a missed disclosure. Balances shown for FY2022 onward are averages of the four quarter-ends preceding each year-end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A9:L9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12053,6 +12235,1306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — UK KM1 Key Metrics Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ICBCS Group (consolidated basis), as published. Amounts in USD millions; ratios as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1 Common Equity Tier 1 (CET1) capital ($m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1819.5</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1676.1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1629.1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1148.4</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2 Tier 1 capital ($m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1979.5</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1836.1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1789.1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1614.6</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1308.4</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3 Total capital ($m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2229.5</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2086.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2039.1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1864.6</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1558.4</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4 Total risk-weighted exposure amount ($m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>14902.7</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>11500.1</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9653.200000000001</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>9251</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>8526.299999999999</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5 Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>12.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6 Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7 Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c Additional T2 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>10.3%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8 Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>UK 8a Conservation buffer due to macro-prudential or systemic risk identified at the level of a Member State (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>9 Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 9a Systemic risk buffer (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>10 Global Systemically Important Institution buffer (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>UK 10a Other Systemically Important Institution buffer</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>11 Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>14.1%</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>12 CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>7.2%</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>9.4%</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>13 Total exposure measure excluding claims on central banks ($m)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>35294.7</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>26624</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>23301</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>20958.2</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>25679.8</v>
+      </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>14 Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>15 Total high-quality liquid assets (HQLA) (Weighted value - average) ($m)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>5294.2</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>5216.2</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>5704.2</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>6280.5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>5026.7</v>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a Cash outflows - Total weighted value ($m)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>11109</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>8275.1</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>8049.2</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>8343</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>9199.299999999999</v>
+      </c>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b Cash inflows - Total weighted value ($m)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>9539.9</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>6036.4</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>4559.5</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>5656.9</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>7290.9</v>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>16 Total net cash outflows (adjusted value) ($m)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>2777.2</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>2422.5</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>3561.5</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>2926.2</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>2425.2</v>
+      </c>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>17 Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>197.3%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>226.7%</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>165.3%</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>206.0%</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>207.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>18 Total available stable funding ($m)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>9393</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>8348.6</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>7963.4</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>8417.6</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8474.799999999999</v>
+      </c>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>19 Total required stable funding ($m)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>7736.7</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>6118.4</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>4462</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>5266.3</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>6955.7</v>
+      </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>20 NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>122.8%</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>136.4%</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>183.3%</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>163.8%</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>121.8%</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+    </row>
+    <row r="43" ht="330" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc's own 'UK KM1 - Key metrics template', reproduced as published. ICBCS Group (consolidated basis), USD millions, the presentation currency of the template itself.
+FY2025 &amp; FY2024 column-header years 2025/2024: Pillar 3 Disclosures 2025, p.5 (Table: UK KM1 - Key metrics template, in section 'Key metrics and overview of risk-weighted exposure amounts') — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2024: Pillar 3 Disclosures 2024, p.5 (UK KM1), its OWN reporting year — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2024pillar3.pdf
+FY2023: Pillar 3 Disclosures 2023, p.5 (UK KM1), its OWN reporting year — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2022: Pillar 3 Disclosures 2022, p.5 (UK KM1), its OWN reporting year — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2022pillar3re-publish.pdf
+FY2021: NOT from a FY2021 KM1 — the Pillar 3 Disclosures 2021 document prints NO UK KM1 template at all (see the sheet note). The FY2021 column here is the 2022 edition's own '31.12.2021' COMPARATIVE column, p.5 — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2022pillar3re-publish.pdf
+Each of FY2025/FY2024/FY2023/FY2022 is taken from the edition in which that year is the REPORTING year, not from a later edition's comparative. Where both were available they were compared and agree digit for digit (e.g. the 2025 edition's 2024 comparative reproduces the 2024 edition's own 2024 column exactly, and the same holds for 2023 in the 2024 edition and 2022 in the 2023 edition).
+Column-header style is the bank's own and changes between editions (the 2022 edition heads its columns '31.12.2022 / 31.12.2021'; the 2023, 2024 and 2025 editions use bare years). Every row number, row label, row order and printed precision below is the bank's own.
+FY2020 AND EARLIER ARE BLANK BECAUSE THE TEMPLATE DOES NOT EXIST IN THOSE EDITIONS, not because it was not found. All eleven ICBC Standard Bank Pillar 3 editions 2015-2025 were downloaded and searched this session. The 2015-2021 editions print no UK KM1 template: what they do print is 'Table 9: IFRS9 Transitionals', a DIFFERENT prescribed template (the IFRS9-FL transitional-arrangements disclosure). It carries seventeen of its own row numbers covering CET1/Tier 1/Total capital, RWAs, the three capital ratios and the leverage ratio, each also shown 'as if IFRS 9 transitional arrangements had not been applied' — but it has NO SREP rows, no buffer rows, no LCR rows and no NSFR rows. On the row-set test it is not the KM1 template, and mapping its rows onto KM1 row numbers would invent a correspondence the bank never published. Those years' figures are on the eleven single-metric sheets instead, sourced from that table and from Table 5 (Capital Resources), as each of those sheets' own notes records.
+FY2021 IS FILLED FROM A COMPARATIVE, AND IS THE ONLY COLUMN ON THIS SHEET THAT IS. The FY2021 edition prints no KM1 at all (above), so there is no own-edition table for that year to displace; the column is the 2022 edition's own 31.12.2021 comparative. It is independently corroborated by the 2021 edition's own Table 9, which prints the same CET1 capital (1,148.4), Tier 1 capital (1,308.4), Total capital (1,558.4), RWAs (8,526.3) and leverage exposure measure (25,679.8) to the same decimal.
+PRECISION DIFFERS BETWEEN THE TWO FY2021 SOURCES AND IS REPRODUCED, NOT RECONCILED. The 2021 edition's Table 9 prints the FY2021 ratios to two decimals (CET1 13.47%, Tier 1 15.35%, Total capital 18.28%, leverage 5.09%) while the 2022 edition's KM1 comparative rounds the same ratios to one (13.5%, 15.4%, 18.3%, 5.1%). This sheet shows the KM1 comparative as the KM1 template printed it; the single-metric sheets show the 2021 edition's own two-decimal figures. Both are the bank's own numbers at different printed precision, and each is left exactly as the document that carries it printed it.
+SOURCE DEFECT RECORDED, NOT CORRECTED: the NSFR sheet in this workbook states that no FY2021 NSFR figure is available because the UK NSFR regime only took effect on 1 January 2022. The 2022 edition's KM1 nevertheless prints a 31.12.2021 NSFR comparative (121.8%, with available/required stable funding of 8,474.8 / 6,955.7). Both statements are the bank's own; the comparative is reproduced here as printed and the NSFR sheet is left as it stands rather than being edited to agree.
+Rows UK 8a, UK 9a, 10 and UK 10a are printed as an explicit '0.0%' in every edition from 2022 onward, not as a dash, so they are recorded as zeros. Rows UK 14a-14e are absent from every edition: each one states in a footnote that they 'have not been disclosed as these are only applicable to LREQ firms', and the 2025 edition adds that ICBCS is out of scope of the PRA's binding leverage ratio requirement by way of a modification by consent. That is a stated exclusion, not a gap.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A43:L43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12214,192 +13696,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A7:L7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>12.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>13.47%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>13.21%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>13.64%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>18.52%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>15.59%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>13.87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
-FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.26 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
-FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.27 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
-FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
-FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
-FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.23 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
-FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
-Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12431,14 +13727,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Tier 1 Capital</t>
+          <t>ICBC Standard Bank Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, $m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -12507,41 +13803,63 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1979.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1836.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1789.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1614.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1308.4</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1232.9</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1108.3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1204</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>1229.5</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>928.6</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1051</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>12.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>13.47%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>13.21%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>13.64%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>18.52%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>15.59%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>13.87%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="100" customHeight="1">

--- a/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
+++ b/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
@@ -12235,7 +12235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -12244,12 +12244,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12295,36 +12289,6 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12303,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -12367,12 +12325,6 @@
       <c r="F5" s="6" t="n">
         <v>1148.4</v>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -12395,12 +12347,6 @@
       <c r="F6" s="6" t="n">
         <v>1308.4</v>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -12423,12 +12369,6 @@
       <c r="F7" s="6" t="n">
         <v>1558.4</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -12441,12 +12381,6 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -12469,12 +12403,6 @@
       <c r="F9" s="6" t="n">
         <v>8526.299999999999</v>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -12487,12 +12415,6 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -12525,12 +12447,6 @@
           <t>13.5%</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12563,12 +12479,6 @@
           <t>15.4%</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -12601,12 +12511,6 @@
           <t>18.3%</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -12619,12 +12523,6 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -12657,12 +12555,6 @@
           <t>1.9%</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -12695,12 +12587,6 @@
           <t>0.6%</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -12733,12 +12619,6 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -12771,12 +12651,6 @@
           <t>11.3%</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -12789,12 +12663,6 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -12827,12 +12695,6 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -12865,12 +12727,6 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -12903,12 +12759,6 @@
           <t>0.1%</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -12941,12 +12791,6 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -12979,12 +12823,6 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -13017,12 +12855,6 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -13055,12 +12887,6 @@
           <t>2.6%</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -13093,12 +12919,6 @@
           <t>13.9%</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13131,12 +12951,6 @@
           <t>7.1%</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -13149,12 +12963,6 @@
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -13177,12 +12985,6 @@
       <c r="F30" s="6" t="n">
         <v>25679.8</v>
       </c>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -13215,12 +13017,6 @@
           <t>5.1%</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -13233,12 +13029,6 @@
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -13261,12 +13051,6 @@
       <c r="F33" s="6" t="n">
         <v>5026.7</v>
       </c>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -13289,12 +13073,6 @@
       <c r="F34" s="6" t="n">
         <v>9199.299999999999</v>
       </c>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -13317,12 +13095,6 @@
       <c r="F35" s="6" t="n">
         <v>7290.9</v>
       </c>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -13345,12 +13117,6 @@
       <c r="F36" s="6" t="n">
         <v>2425.2</v>
       </c>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -13383,12 +13149,6 @@
           <t>207.3%</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -13401,12 +13161,6 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -13429,12 +13183,6 @@
       <c r="F39" s="6" t="n">
         <v>8474.799999999999</v>
       </c>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -13457,12 +13205,6 @@
       <c r="F40" s="6" t="n">
         <v>6955.7</v>
       </c>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
-      <c r="I40" s="6" t="n"/>
-      <c r="J40" s="6" t="n"/>
-      <c r="K40" s="6" t="n"/>
-      <c r="L40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -13495,12 +13237,6 @@
           <t>121.8%</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
     </row>
     <row r="43" ht="330" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
@@ -13523,7 +13259,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
+++ b/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
@@ -1742,6 +1742,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2433,6 +2434,9 @@
           <t>NSFR</t>
         </is>
       </c>
+      <c r="BZ11" t="n">
+        <v>121.8</v>
+      </c>
       <c r="CA11" t="n">
         <v>163.8</v>
       </c>
@@ -3998,7 +4002,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -5907,7 +5911,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – FY2015 Pillar 3 (PDF p.28) treats the LCR qualitatively; FY2015 Annual Report (p.134) says only that it was 'in excess of 100%'</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6065,9 @@
       <c r="E4" s="6" t="n">
         <v>8417.6</v>
       </c>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="6" t="n">
+        <v>8474.799999999999</v>
+      </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
@@ -6087,7 +6093,9 @@
       <c r="E5" s="6" t="n">
         <v>5266.3</v>
       </c>
-      <c r="F5" s="6" t="n"/>
+      <c r="F5" s="6" t="n">
+        <v>6955.7</v>
+      </c>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
@@ -6123,37 +6131,37 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – no NSFR figure in the FY2020 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – no NSFR figure in the FY2019 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – no NSFR figure in the FY2018 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – no NSFR figure in the FY2017 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – no NSFR figure in the FY2016 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – no NSFR figure in the FY2015 Pillar 3 (text-searched 2026-09-19; narrative only: 'expected to go live in January 2018'); UK NSFR applied from 1 Jan 2022</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6169,8 @@
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: OMISSION CORRECTED 2026-09-17 (KM1-017): the four NSFR percentages for FY2025-FY2022 were MISSING from this sheet until this ticket. The available and required stable funding amounts were present for those four years but the ratio row carried no value for any of them - it was built from a comprehension that assigned 'Not disclosed' to every year EXCEPT FY2025-FY2022, and then never assigned those four anything at all, so they rendered blank. The bank does disclose them: they are row 20 of its own UK KM1 template in each year's edition (FY2025 122.8%, FY2024 136.4%, FY2023 183.3%, FY2022 163.8%), the same table this workbook's KM1 Key Metrics sheet reproduces and the same table the stable-funding amounts on the rows above already came from. Nothing was re-derived: each figure is transcribed from the edition in which that year is the reporting year. The omission came to light on 2026-09-17, when this workbook gained a KM1 Key Metrics sheet reproducing row 20 of the same table for the same years and so placed a second, independent transcription of each of those four figures beside this sheet's.
-NSFR was not a UK Pillar 3 disclosure requirement until 1 January 2022 (the UK NSFR regime's effective date), so no FY2015-FY2021 figures are available in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025). FY2015's own Pillar 3 document explicitly notes 'the NSFR is expected to go live in January 2018' (an EU timeline later superseded by the UK's own 1 January 2022 implementation) - confirming this is a genuine regulatory-timeline gap, not a missed disclosure. Balances shown for FY2022 onward are averages of the four quarter-ends preceding each year-end.</t>
+FY2021 (ASF 8,474.8 / RSF 6,955.7 / NSFR 121.8%) ADDED 2026-09-19 (GA-020) from the 31.12.2021 comparative column of UK KM1 rows 18-20, p.5 of the 2022 Pillar 3 Disclosures (https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2022pillar3re-publish.pdf), read off the page image. BASIS DIFFERS FROM THE COLUMNS BESIDE IT, as the template's own footnote 2 says: '2021 numbers are spot values as at 31 December 2021 as NSFR went live from 1 January 2022', whereas FY2022 onward are four-quarter averages. The 2021 edition itself prints no NSFR figure (its three NSFR mentions are narrative), so this is the only published FY2021 value. This also removes the disagreement the KM1 sheet's note recorded between that sheet's row 20 and this one.
+NSFR was not a UK Pillar 3 disclosure requirement until 1 January 2022 (the UK NSFR regime's effective date), so no FY2015-FY2020 figures are available in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025). FY2015's own Pillar 3 document explicitly notes 'the NSFR is expected to go live in January 2018' (an EU timeline later superseded by the UK's own 1 January 2022 implementation) - confirming this is a genuine regulatory-timeline gap, not a missed disclosure. Balances shown for FY2022 onward are averages of the four quarter-ends preceding each year-end.</t>
         </is>
       </c>
     </row>
@@ -6291,64 +6300,64 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: No MREL disclosure appears in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025) — ICBC Standard Bank Plc is not itself a resolution entity subject to a standalone MREL requirement.</t>
+          <t>Note: No MREL disclosure appears in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports (2015-2025): each was re-fetched from its cited URL and text-searched on 2026-09-19, and 'MREL' returns zero hits in every one. An earlier version of this note added that ICBC Standard Bank Plc is not itself a resolution entity subject to a standalone MREL requirement; no document stating that was cited, so the cells rest on the absence alone.</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13261,7 @@
 FY2020 AND EARLIER ARE BLANK BECAUSE THE TEMPLATE DOES NOT EXIST IN THOSE EDITIONS, not because it was not found. All eleven ICBC Standard Bank Pillar 3 editions 2015-2025 were downloaded and searched this session. The 2015-2021 editions print no UK KM1 template: what they do print is 'Table 9: IFRS9 Transitionals', a DIFFERENT prescribed template (the IFRS9-FL transitional-arrangements disclosure). It carries seventeen of its own row numbers covering CET1/Tier 1/Total capital, RWAs, the three capital ratios and the leverage ratio, each also shown 'as if IFRS 9 transitional arrangements had not been applied' — but it has NO SREP rows, no buffer rows, no LCR rows and no NSFR rows. On the row-set test it is not the KM1 template, and mapping its rows onto KM1 row numbers would invent a correspondence the bank never published. Those years' figures are on the eleven single-metric sheets instead, sourced from that table and from Table 5 (Capital Resources), as each of those sheets' own notes records.
 FY2021 IS FILLED FROM A COMPARATIVE, AND IS THE ONLY COLUMN ON THIS SHEET THAT IS. The FY2021 edition prints no KM1 at all (above), so there is no own-edition table for that year to displace; the column is the 2022 edition's own 31.12.2021 comparative. It is independently corroborated by the 2021 edition's own Table 9, which prints the same CET1 capital (1,148.4), Tier 1 capital (1,308.4), Total capital (1,558.4), RWAs (8,526.3) and leverage exposure measure (25,679.8) to the same decimal.
 PRECISION DIFFERS BETWEEN THE TWO FY2021 SOURCES AND IS REPRODUCED, NOT RECONCILED. The 2021 edition's Table 9 prints the FY2021 ratios to two decimals (CET1 13.47%, Tier 1 15.35%, Total capital 18.28%, leverage 5.09%) while the 2022 edition's KM1 comparative rounds the same ratios to one (13.5%, 15.4%, 18.3%, 5.1%). This sheet shows the KM1 comparative as the KM1 template printed it; the single-metric sheets show the 2021 edition's own two-decimal figures. Both are the bank's own numbers at different printed precision, and each is left exactly as the document that carries it printed it.
-SOURCE DEFECT RECORDED, NOT CORRECTED: the NSFR sheet in this workbook states that no FY2021 NSFR figure is available because the UK NSFR regime only took effect on 1 January 2022. The 2022 edition's KM1 nevertheless prints a 31.12.2021 NSFR comparative (121.8%, with available/required stable funding of 8,474.8 / 6,955.7). Both statements are the bank's own; the comparative is reproduced here as printed and the NSFR sheet is left as it stands rather than being edited to agree.
+FY2021 NSFR: the 2022 edition's KM1 prints a 31.12.2021 NSFR comparative (121.8%, with available/required stable funding of 8,474.8 / 6,955.7), footnoted as SPOT values because the NSFR went live on 1 January 2022. The NSFR sheet previously said no FY2021 figure was available; since 2026-09-19 (GA-020) it carries these same three figures from this same page, with the spot-basis caveat, so the two sheets now agree.
 Rows UK 8a, UK 9a, 10 and UK 10a are printed as an explicit '0.0%' in every edition from 2022 onward, not as a dash, so they are recorded as zeros. Rows UK 14a-14e are absent from every edition: each one states in a footnote that they 'have not been disclosed as these are only applicable to LREQ firms', and the 2025 edition adds that ICBCS is out of scope of the PRA's binding leverage ratio requirement by way of a modification by consent. That is a stated exclusion, not a gap.</t>
         </is>
       </c>

--- a/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
+++ b/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – FY2015 Pillar 3 (PDF p.28) treats the LCR qualitatively; FY2015 Annual Report (p.134) says only that it was 'in excess of 100%'</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="39" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. All amounts are in USD ($m), the reporting currency used throughout ICBC Standard Bank Plc's Annual Reports and Pillar 3 Disclosures. FY2015 is the entity's genuine historical floor (ICBC Standard Bank Plc was created 1 February 2015); pre-2018 figures reflect IAS 39 accounting and Basel III's transitional (non-KM1-template) Pillar 3 disclosure format - see the Balance Sheet, Profit &amp; Loss, Asset Quality and Pillar 3 metric sheets' own source notes for the specific terminology/basis shifts (IAS 39→IFRS 9 in 2018, no Additional Tier 1 capital before December 2019, no UK NSFR requirement before 2022).</t>
@@ -4191,7 +4191,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -4377,14 +4377,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row; same for FY2020-FY2015. Tier 1 ratio equals the CET1 ratio exactly for FY2015-FY2018 (no Additional Tier 1 capital existed yet).</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="169" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -4549,14 +4549,14 @@
         <v>1449.6</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021-FY2015 figures are each year's own 'Total eligible capital' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="169" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -4743,14 +4743,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021-FY2015 figures are each year's own 'Capital Adequacy ratio' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="169" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -4915,7 +4915,7 @@
         <v>7579.7</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -5423,7 +5423,7 @@
         <v>7579.7</v>
       </c>
     </row>
-    <row r="17" ht="150" customHeight="1">
+    <row r="17" ht="182" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
@@ -5649,14 +5649,17 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021-FY2015 all use the CRR Leverage Ratio Common Disclosure Template's 'Total leverage ratio exposures' and 'Leverage ratio' rows (Annex D) — the pre-'excluding central banks' presentation format used before the later UK KM1 template split the exposure measure basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1">
+          <t xml:space="preserve">Note: FY2021-FY2015 all use the CRR Leverage Ratio Common Disclosure Template's 'Total leverage ratio exposures' and 'Leverage ratio' rows (Annex D) — the pre-'excluding central banks' presentation format used before the later UK KM1 template split the exposure measure basis.
+ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
+HOW THAT WAS ESTABLISHED: all 10 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (10 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. Every match was opened and read on 2026-10-09; none is an in-scope disclosure. In PRE-2022 editions the hit is the OLD CRR 'Leverage ratio common disclosure', not the UK dual-basis template: it prints a single 'Leverage ratio total exposure measure' with no excluding/including split, which is why those same documents carry no 'excluding claims on central banks' wording either. The UK split took effect only for periods from 1 January 2022, so those editions confirm the dual basis did not yet exist rather than offering a figure to carry. The remaining matches are NOT leverage at all: template UK CC1 (composition of regulatory own funds) has its own rows UK-25a 'Losses for the current financial year' and UK-25b 'Foreseeable tax charges', which collide with the leverage template's UK-25a/UK-25c row numbering. A row number alone never identifies a template. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
+THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="169" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -5915,14 +5918,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: LCR figures are averages of month-end observations over the 12 months preceding each year-end. FY2021-FY2017 figures are each year's own 31 December quarter-end column of the 'Consolidated Liquidity Coverage Ratio for ICBCS (Group)' table, the same consolidated-Group basis used by the later UK KM1 template rows. FY2016's Pillar 3 document discloses only a single point-in-time LCR% as at 31 December 2016 (159%, PRA minimum 80% that year) with no HQLA/net-outflow $ breakdown and not framed as a 12-month average - a narrower disclosure format than later years', shown with blank $m cells rather than a fabricated breakdown. FY2015's Pillar 3 document discusses the LCR requirement only qualitatively, with no numeric LCR%, HQLA or net-outflow figure disclosed at all that year (the EBA/PRA quarterly LCR disclosure tables used from FY2017 onward were not yet in place) - a genuine self-skip, not a search failure.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="100" customHeight="1">
+    <row r="9" ht="169" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -6165,7 +6168,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: OMISSION CORRECTED 2026-09-17 (KM1-017): the four NSFR percentages for FY2025-FY2022 were MISSING from this sheet until this ticket. The available and required stable funding amounts were present for those four years but the ratio row carried no value for any of them - it was built from a comprehension that assigned 'Not disclosed' to every year EXCEPT FY2025-FY2022, and then never assigned those four anything at all, so they rendered blank. The bank does disclose them: they are row 20 of its own UK KM1 template in each year's edition (FY2025 122.8%, FY2024 136.4%, FY2023 183.3%, FY2022 163.8%), the same table this workbook's KM1 Key Metrics sheet reproduces and the same table the stable-funding amounts on the rows above already came from. Nothing was re-derived: each figure is transcribed from the edition in which that year is the reporting year. The omission came to light on 2026-09-17, when this workbook gained a KM1 Key Metrics sheet reproducing row 20 of the same table for the same years and so placed a second, independent transcription of each of those four figures beside this sheet's.
@@ -6354,7 +6357,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: No MREL disclosure appears in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports (2015-2025): each was re-fetched from its cited URL and text-searched on 2026-09-19, and 'MREL' returns zero hits in every one. An earlier version of this note added that ICBC Standard Bank Plc is not itself a resolution entity subject to a standalone MREL requirement; no document stating that was cited, so the cells rest on the absence alone.</t>
@@ -7669,7 +7672,7 @@
         <v>20137.5</v>
       </c>
     </row>
-    <row r="37" ht="110" customHeight="1">
+    <row r="37" ht="195" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
@@ -8957,7 +8960,7 @@
         <v>-281</v>
       </c>
     </row>
-    <row r="38" ht="130" customHeight="1">
+    <row r="38" ht="221" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
@@ -10015,7 +10018,7 @@
         <v>2131.4</v>
       </c>
     </row>
-    <row r="41" ht="140" customHeight="1">
+    <row r="41" ht="221" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
@@ -11549,7 +11552,7 @@
         <v>4476.2</v>
       </c>
     </row>
-    <row r="50" ht="110" customHeight="1">
+    <row r="50" ht="195" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Sources — all figures are ICBC Standard Bank Plc consolidated (Group) statement of cash flows, $m:
@@ -12213,7 +12216,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="24" ht="140" customHeight="1">
+    <row r="24" ht="208" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Sources — All figures are ICBC Standard Bank Plc consolidated (Group) basis, $m unless stated, each year's own originally-published figures (not a later restated comparative). ICBCS is jointly owned by Industrial and Commercial Bank of China Limited (60%) and Standard Bank Group Limited (40%).
@@ -12244,7 +12247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -13247,7 +13250,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="330" customHeight="1">
+    <row r="43" ht="377" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc's own 'UK KM1 - Key metrics template', reproduced as published. ICBCS Group (consolidated basis), USD millions, the presentation currency of the template itself.
@@ -13261,13 +13264,21 @@
 FY2020 AND EARLIER ARE BLANK BECAUSE THE TEMPLATE DOES NOT EXIST IN THOSE EDITIONS, not because it was not found. All eleven ICBC Standard Bank Pillar 3 editions 2015-2025 were downloaded and searched this session. The 2015-2021 editions print no UK KM1 template: what they do print is 'Table 9: IFRS9 Transitionals', a DIFFERENT prescribed template (the IFRS9-FL transitional-arrangements disclosure). It carries seventeen of its own row numbers covering CET1/Tier 1/Total capital, RWAs, the three capital ratios and the leverage ratio, each also shown 'as if IFRS 9 transitional arrangements had not been applied' — but it has NO SREP rows, no buffer rows, no LCR rows and no NSFR rows. On the row-set test it is not the KM1 template, and mapping its rows onto KM1 row numbers would invent a correspondence the bank never published. Those years' figures are on the eleven single-metric sheets instead, sourced from that table and from Table 5 (Capital Resources), as each of those sheets' own notes records.
 FY2021 IS FILLED FROM A COMPARATIVE, AND IS THE ONLY COLUMN ON THIS SHEET THAT IS. The FY2021 edition prints no KM1 at all (above), so there is no own-edition table for that year to displace; the column is the 2022 edition's own 31.12.2021 comparative. It is independently corroborated by the 2021 edition's own Table 9, which prints the same CET1 capital (1,148.4), Tier 1 capital (1,308.4), Total capital (1,558.4), RWAs (8,526.3) and leverage exposure measure (25,679.8) to the same decimal.
 PRECISION DIFFERS BETWEEN THE TWO FY2021 SOURCES AND IS REPRODUCED, NOT RECONCILED. The 2021 edition's Table 9 prints the FY2021 ratios to two decimals (CET1 13.47%, Tier 1 15.35%, Total capital 18.28%, leverage 5.09%) while the 2022 edition's KM1 comparative rounds the same ratios to one (13.5%, 15.4%, 18.3%, 5.1%). This sheet shows the KM1 comparative as the KM1 template printed it; the single-metric sheets show the 2021 edition's own two-decimal figures. Both are the bank's own numbers at different printed precision, and each is left exactly as the document that carries it printed it.
-FY2021 NSFR: the 2022 edition's KM1 prints a 31.12.2021 NSFR comparative (121.8%, with available/required stable funding of 8,474.8 / 6,955.7), footnoted as SPOT values because the NSFR went live on 1 January 2022. The NSFR sheet previously said no FY2021 figure was available; since 2026-09-19 (GA-020) it carries these same three figures from this same page, with the spot-basis caveat, so the two sheets now agree.
+FY2021 NSFR: the 2022 edition's KM1 prints a 31.12.2021 NSFR comparative (121.8%, with available/required stable funding of 8,474.8 / 6,955.7), footnoted as SPOT values because the NSFR went live on 1 January 2022. The NSFR sheet previously said no FY2021 figure was available; since 2026-09-19 (GA-020) it carries these same three figures from this same page, with the spot-basis caveat, so the two sheets now agree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="330" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 Rows UK 8a, UK 9a, 10 and UK 10a are printed as an explicit '0.0%' in every edition from 2022 onward, not as a dash, so they are recorded as zeros. Rows UK 14a-14e are absent from every edition: each one states in a footnote that they 'have not been disclosed as these are only applicable to LREQ firms', and the 2025 edition adds that ICBCS is out of scope of the PRA's binding leverage ratio requirement by way of a modification by consent. That is a stated exclusion, not a gap.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13413,14 +13424,14 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021-FY2015 figures are each year's own 'Total Common Equity Tier I' from that year's Table 5 (Capital Resources), the transitional-basis equivalent of the UK KM1 template row used from FY2022 onward. Additional Tier 1 capital did not exist before a $160.0m issuance to ICBC in December 2019, so CET1 capital equals Tier 1 capital exactly for FY2015-FY2018.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="169" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
@@ -13607,7 +13618,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="169" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:

--- a/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
+++ b/banks/ICBC STANDARD BANK PLC FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4078,14 +4079,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Tier 1 Capital</t>
+          <t>ICBC Standard Bank Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, $m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -4154,41 +4155,63 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1979.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1836.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1789.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1614.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1308.4</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1232.9</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1108.3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1204</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>1229.5</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>928.6</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1051</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>12.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>13.47%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>13.21%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>13.64%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>18.52%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>15.59%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>13.87%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="169" customHeight="1">
@@ -4222,7 +4245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4242,14 +4265,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Tier 1 Ratio</t>
+          <t>ICBC Standard Bank Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, $m</t>
         </is>
       </c>
     </row>
@@ -4318,74 +4341,45 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>15.35%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>15.94%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>18.52%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>15.59%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row; same for FY2020-FY2015. Tier 1 ratio equals the CET1 ratio exactly for FY2015-FY2018 (no Additional Tier 1 capital existed yet).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="169" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1979.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1836.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1789.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1614.6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1308.4</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1232.9</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1108.3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>928.6</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="6" ht="169" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
@@ -4402,9 +4396,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A7:L7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4436,14 +4429,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total Capital</t>
+          <t>ICBC Standard Bank Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, $m</t>
+          <t>Consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -4512,47 +4505,69 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>2229.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>2086.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>2039.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1864.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1558.4</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1482.9</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1358.3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1446.1</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>1575.4</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>1227.3</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1449.6</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>15.18%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>15.94%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>18.52%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>15.59%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021-FY2015 figures are each year's own 'Total eligible capital' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+          <t>Note: FY2021 figure is 'Tier 1 Risk Asset Ratio' from Table 5, the transitional-basis equivalent of the later UK KM1 template row; same for FY2020-FY2015. Tier 1 ratio equals the CET1 ratio exactly for FY2015-FY2018 (no Additional Tier 1 capital existed yet).</t>
         </is>
       </c>
     </row>
@@ -4608,14 +4623,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — Total Capital Ratio</t>
+          <t>ICBC Standard Bank Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis, % of RWA</t>
+          <t>Consolidated basis, $m</t>
         </is>
       </c>
     </row>
@@ -4684,69 +4699,47 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>21.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.28%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>18.26%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>19.54%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>22.25%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>19.97%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>19.3%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>19.13%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2229.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2086.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2039.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1864.6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1558.4</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1482.9</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1358.3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1446.1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1575.4</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>1227.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1449.6</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021-FY2015 figures are each year's own 'Capital Adequacy ratio' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+          <t>Note: FY2021-FY2015 figures are each year's own 'Total eligible capital' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
         </is>
       </c>
     </row>
@@ -4777,6 +4770,200 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.28%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>18.26%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>19.54%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>22.25%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>19.97%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>19.3%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>19.13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021-FY2015 figures are each year's own 'Capital Adequacy ratio' from that year's Table 5, the transitional-basis equivalent of the later UK KM1 template row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="169" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
+FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.26 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
+FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.27 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
+FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
+FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
+FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.23 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
+FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
+Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A7:L7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4940,7 +5127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5448,7 +5635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5680,272 +5867,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A6:L6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, $m / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value (average) ($m)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>5294.2</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>5216.2</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>5704.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>6280.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>5027</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>4371</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>4856</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>4458</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>4322</v>
-      </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value ($m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>2777.2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>2422.5</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>2926.2</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2425</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>2426</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>2509</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>2062</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>3126</v>
-      </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>197.3%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>226.7%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>165.3%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>206.0%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>207%</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>180%</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>195%</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>217%</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>145%</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>159%</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>Not published – FY2015 Pillar 3 (PDF p.28) treats the LCR qualitatively; FY2015 Annual Report (p.134) says only that it was 'in excess of 100%'</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: LCR figures are averages of month-end observations over the 12 months preceding each year-end. FY2021-FY2017 figures are each year's own 31 December quarter-end column of the 'Consolidated Liquidity Coverage Ratio for ICBCS (Group)' table, the same consolidated-Group basis used by the later UK KM1 template rows. FY2016's Pillar 3 document discloses only a single point-in-time LCR% as at 31 December 2016 (159%, PRA minimum 80% that year) with no HQLA/net-outflow $ breakdown and not framed as a 12-month average - a narrower disclosure format than later years', shown with blank $m cells rather than a fabricated breakdown. FY2015's Pillar 3 document discusses the LCR requirement only qualitatively, with no numeric LCR%, HQLA or net-outflow figure disclosed at all that year (the EBA/PRA quarterly LCR disclosure tables used from FY2017 onward were not yet in place) - a genuine self-skip, not a search failure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="169" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
-FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
-FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.31 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
-FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.29 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
-FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
-FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
-FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
-Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A9:L9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5977,7 +5898,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — NSFR</t>
+          <t>ICBC Standard Bank Plc — LCR</t>
         </is>
       </c>
     </row>
@@ -6053,137 +5974,158 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding ($m)</t>
+          <t>Total high-quality liquid assets (HQLA), weighted value (average) ($m)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9393</v>
+        <v>5294.2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8348.6</v>
+        <v>5216.2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7963.4</v>
+        <v>5704.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>8417.6</v>
+        <v>6280.5</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>8474.799999999999</v>
-      </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
+        <v>5027</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4371</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4856</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4458</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>4322</v>
+      </c>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding ($m)</t>
+          <t>Total net cash outflows, adjusted value ($m)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>7736.7</v>
+        <v>2777.2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6118.4</v>
+        <v>2422.5</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4462</v>
+        <v>3561.5</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>5266.3</v>
+        <v>2926.2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>6955.7</v>
-      </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
+        <v>2425</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>2426</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>2509</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>2062</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>3126</v>
+      </c>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (%)</t>
+          <t>Liquidity Coverage Ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>197.3%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>136.4%</t>
+          <t>226.7%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>183.3%</t>
+          <t>165.3%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>163.8%</t>
+          <t>206.0%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>121.8%</t>
+          <t>207%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Not published – no NSFR figure in the FY2020 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Not published – no NSFR figure in the FY2019 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+          <t>195%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Not published – no NSFR figure in the FY2018 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+          <t>217%</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Not published – no NSFR figure in the FY2017 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+          <t>145%</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Not published – no NSFR figure in the FY2016 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+          <t>159%</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Not published – no NSFR figure in the FY2015 Pillar 3 (text-searched 2026-09-19; narrative only: 'expected to go live in January 2018'); UK NSFR applied from 1 Jan 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
+          <t>Not published – FY2015 Pillar 3 (PDF p.28) treats the LCR qualitatively; FY2015 Annual Report (p.134) says only that it was 'in excess of 100%'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: OMISSION CORRECTED 2026-09-17 (KM1-017): the four NSFR percentages for FY2025-FY2022 were MISSING from this sheet until this ticket. The available and required stable funding amounts were present for those four years but the ratio row carried no value for any of them - it was built from a comprehension that assigned 'Not disclosed' to every year EXCEPT FY2025-FY2022, and then never assigned those four anything at all, so they rendered blank. The bank does disclose them: they are row 20 of its own UK KM1 template in each year's edition (FY2025 122.8%, FY2024 136.4%, FY2023 183.3%, FY2022 163.8%), the same table this workbook's KM1 Key Metrics sheet reproduces and the same table the stable-funding amounts on the rows above already came from. Nothing was re-derived: each figure is transcribed from the edition in which that year is the reporting year. The omission came to light on 2026-09-17, when this workbook gained a KM1 Key Metrics sheet reproducing row 20 of the same table for the same years and so placed a second, independent transcription of each of those four figures beside this sheet's.
-FY2021 (ASF 8,474.8 / RSF 6,955.7 / NSFR 121.8%) ADDED 2026-09-19 (GA-020) from the 31.12.2021 comparative column of UK KM1 rows 18-20, p.5 of the 2022 Pillar 3 Disclosures (https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2022pillar3re-publish.pdf), read off the page image. BASIS DIFFERS FROM THE COLUMNS BESIDE IT, as the template's own footnote 2 says: '2021 numbers are spot values as at 31 December 2021 as NSFR went live from 1 January 2022', whereas FY2022 onward are four-quarter averages. The 2021 edition itself prints no NSFR figure (its three NSFR mentions are narrative), so this is the only published FY2021 value. This also removes the disagreement the KM1 sheet's note recorded between that sheet's row 20 and this one.
-NSFR was not a UK Pillar 3 disclosure requirement until 1 January 2022 (the UK NSFR regime's effective date), so no FY2015-FY2020 figures are available in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025). FY2015's own Pillar 3 document explicitly notes 'the NSFR is expected to go live in January 2018' (an EU timeline later superseded by the UK's own 1 January 2022 implementation) - confirming this is a genuine regulatory-timeline gap, not a missed disclosure. Balances shown for FY2022 onward are averages of the four quarter-ends preceding each year-end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
+          <t>Note: LCR figures are averages of month-end observations over the 12 months preceding each year-end. FY2021-FY2017 figures are each year's own 31 December quarter-end column of the 'Consolidated Liquidity Coverage Ratio for ICBCS (Group)' table, the same consolidated-Group basis used by the later UK KM1 template rows. FY2016's Pillar 3 document discloses only a single point-in-time LCR% as at 31 December 2016 (159%, PRA minimum 80% that year) with no HQLA/net-outflow $ breakdown and not framed as a 12-month average - a narrower disclosure format than later years', shown with blank $m cells rather than a fabricated breakdown. FY2015's Pillar 3 document discusses the LCR requirement only qualitatively, with no numeric LCR%, HQLA or net-outflow figure disclosed at all that year (the EBA/PRA quarterly LCR disclosure tables used from FY2017 onward were not yet in place) - a genuine self-skip, not a search failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="169" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
 FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
+FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
+FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.31 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
+FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.29 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
+FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.30 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
+FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
+FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.27 (Table 8/9/10: Consolidated Liquidity Coverage Ratio for ICBCS (Group)) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
+Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6222,14 +6164,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICBC Standard Bank Plc — MREL Ratio</t>
+          <t>ICBC Standard Bank Plc — NSFR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated basis</t>
+          <t>Consolidated basis, $m / %</t>
         </is>
       </c>
     </row>
@@ -6298,74 +6240,132 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No MREL disclosure appears in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports (2015-2025): each was re-fetched from its cited URL and text-searched on 2026-09-19, and 'MREL' returns zero hits in every one. An earlier version of this note added that ICBC Standard Bank Plc is not itself a resolution entity subject to a standalone MREL requirement; no document stating that was cited, so the cells rest on the absence alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Total available stable funding ($m)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>9393</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8348.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7963.4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>8417.6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>8474.799999999999</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding ($m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>7736.7</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6118.4</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4462</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5266.3</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>6955.7</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>122.8%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>136.4%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>183.3%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>163.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>121.8%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no NSFR figure in the FY2020 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no NSFR figure in the FY2019 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no NSFR figure in the FY2018 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no NSFR figure in the FY2017 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no NSFR figure in the FY2016 Pillar 3 (text-searched 2026-09-19); UK NSFR applied from 1 Jan 2022</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no NSFR figure in the FY2015 Pillar 3 (text-searched 2026-09-19; narrative only: 'expected to go live in January 2018'); UK NSFR applied from 1 Jan 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: OMISSION CORRECTED 2026-09-17 (KM1-017): the four NSFR percentages for FY2025-FY2022 were MISSING from this sheet until this ticket. The available and required stable funding amounts were present for those four years but the ratio row carried no value for any of them - it was built from a comprehension that assigned 'Not disclosed' to every year EXCEPT FY2025-FY2022, and then never assigned those four anything at all, so they rendered blank. The bank does disclose them: they are row 20 of its own UK KM1 template in each year's edition (FY2025 122.8%, FY2024 136.4%, FY2023 183.3%, FY2022 163.8%), the same table this workbook's KM1 Key Metrics sheet reproduces and the same table the stable-funding amounts on the rows above already came from. Nothing was re-derived: each figure is transcribed from the edition in which that year is the reporting year. The omission came to light on 2026-09-17, when this workbook gained a KM1 Key Metrics sheet reproducing row 20 of the same table for the same years and so placed a second, independent transcription of each of those four figures beside this sheet's.
+FY2021 (ASF 8,474.8 / RSF 6,955.7 / NSFR 121.8%) ADDED 2026-09-19 (GA-020) from the 31.12.2021 comparative column of UK KM1 rows 18-20, p.5 of the 2022 Pillar 3 Disclosures (https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2022pillar3re-publish.pdf), read off the page image. BASIS DIFFERS FROM THE COLUMNS BESIDE IT, as the template's own footnote 2 says: '2021 numbers are spot values as at 31 December 2021 as NSFR went live from 1 January 2022', whereas FY2022 onward are four-quarter averages. The 2021 edition itself prints no NSFR figure (its three NSFR mentions are narrative), so this is the only published FY2021 value. This also removes the disagreement the KM1 sheet's note recorded between that sheet's row 20 and this one.
+NSFR was not a UK Pillar 3 disclosure requirement until 1 January 2022 (the UK NSFR regime's effective date), so no FY2015-FY2020 figures are available in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports reviewed (2015-2025). FY2015's own Pillar 3 document explicitly notes 'the NSFR is expected to go live in January 2018' (an EU timeline later superseded by the UK's own 1 January 2022 implementation) - confirming this is a genuine regulatory-timeline gap, not a missed disclosure. Balances shown for FY2022 onward are averages of the four quarter-ends preceding each year-end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
 FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
@@ -6376,8 +6376,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:L5"/>
     <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A9:L9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7692,6 +7692,193 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A37:L37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in any ICBCS Pillar 3 (all 11 editions 2015-2025 text-searched 2026-09-19: 'MREL' 0 hits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No MREL disclosure appears in any of the eleven ICBC Standard Bank Pillar 3 Disclosures reports (2015-2025): each was re-fetched from its cited URL and text-searched on 2026-09-19, and 'MREL' returns zero hits in every one. An earlier version of this note added that ICBC Standard Bank Plc is not itself a resolution entity subject to a standalone MREL requirement; no document stating that was cited, so the cells rest on the absence alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
+FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
+FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
+FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12247,6 +12434,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ICBC Standard Bank Plc — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>11.04%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>8.21%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>10.53%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.78%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>9.33%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>-20.42%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>-9.72%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>10.55%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>8.05%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>18.85%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>7.20%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>8.87%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>-21.15%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>-1.18%</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>-10.33%</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>-24.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>-1.01%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>-1.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="182" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Return on equity: the document states no definition, and none is supplied here.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2022, where return on equity is 20.78% on an average basis and 18.85% on a year-end basis.
+FY2015 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2015 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2015 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2020 Return on equity 9.4%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit attributable to equity shareholders” and the Balance Sheet rows “total equity (attributable to ordinary shareholders)” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from ICBC Standard Bank Plc's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from ICBC Standard Bank Plc's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘ICBC STANDARD BANK PLC’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A9:L9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13285,7 +13865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13455,190 +14035,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ICBC Standard Bank Plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>12.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>13.47%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>13.21%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>13.64%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>18.52%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>15.59%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>13.87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="169" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — ICBC Standard Bank Plc (ICBCS Group) consolidated (Pillar 3) basis:
-FY2025 &amp; FY2024: ICBC Standard Bank Pillar 3 Disclosures 2025, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2025pillar3disclosures.pdf
-FY2023 &amp; FY2022: ICBC Standard Bank Pillar 3 Disclosures 2023, p.5 (UK KM1 - Key metrics template) — https://v.icbc.com.cn/userfiles/resources/icbc/haiwai/standardbank/download/2023/2023pillar3.pdf
-FY2021: ICBC Standard Bank Pillar 3 Disclosures 2021, p.23 (Table 5: ICBCS - Capital Resources), p.87 (Annex D: Leverage Ratio Common Disclosure Template), p.28 (Table 8: Average Consolidated Liquidity Coverage Ratio for ICBCS Group) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2022/2021_Pillar_3_document.pdf
-FY2020: ICBC Standard Bank Pillar 3 Disclosures 2020, p.26 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2021/2020Pillar3.pdf
-FY2019: ICBC Standard Bank Pillar 3 Disclosures 2019, p.27 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2020/Pillar3Disclosures19.pdf
-FY2018: ICBC Standard Bank Pillar 3 Disclosures 2018, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2018.pdf
-FY2017: ICBC Standard Bank Pillar 3 Disclosures 2017, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar_3_Disclosures_2017.pdf
-FY2016: ICBC Standard Bank Pillar 3 Disclosures 2016, p.23 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/Pillar3Disclosures2016.pdf
-FY2015: ICBC Standard Bank Pillar 3 Disclosures 2015, p.25 (Table 5: ICBCS - Capital Resources) — https://v.icbc.com.cn/userfiles/Resources/ICBC/haiwai/StandardBank/Download/2019/ICBCS_Pillar_3_2015.pdf
-Caveat: Additional Tier 1 capital did not exist in ICBCS's structure until a $160.0m AT1 issuance to ICBC in December 2019 - for FY2015-FY2018, Total Tier 1 capital equals CET1 capital exactly (Additional Tier 1 is nil), and the 'Tier 1 ratio'/'CET1 ratio' rows are numerically identical for those years.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:L6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>